--- a/inventory/files/2026-W42/STA_US_PRIS_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_US_PRIS_2026-W42.xlsx
@@ -1536,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="28" min="1" max="1"/>
@@ -1688,31 +1688,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>USS-2603A</t>
+          <t>PSS-11248A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>284</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PPS-2974A</t>
+          <t>USS-2603A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PSS-11248A</t>
+          <t>PPS-2974A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1742,27 +1742,27 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PPS-4442A</t>
+          <t>PSS-5690A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PSS-5690A</t>
+          <t>PPS-4442A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>USS-1522A</t>
+          <t>PSS-11181A</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1808,21 +1808,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ESS-11151A</t>
+          <t>USS-1522A</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PMB-6889</t>
+          <t>ESS-11151A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1832,7 +1832,17 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PMB-6889</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
